--- a/Data/Figure 3/Mouse weight & GTT/Weight&GTTCohort3.xlsx
+++ b/Data/Figure 3/Mouse weight & GTT/Weight&GTTCohort3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://api.box.com/wopi/files/2122077899296/WOPIServiceId_TP_BOX_2/WOPIUserId_-/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026\Data\Figure 3\Mouse weight &amp; GTT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{992F4810-1F4B-4B50-AAEF-33C8EB3B644F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F465E02-542E-4646-A5F7-537CCFEA86CE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D44538-31DE-4864-BDE3-543D651FBA19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A514A187-A7D1-4A2E-BBE9-38EB1CA0002D}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="36">
   <si>
     <t>Weight</t>
   </si>
@@ -49,66 +49,6 @@
   </si>
   <si>
     <t>Group</t>
-  </si>
-  <si>
-    <t>M1-C5</t>
-  </si>
-  <si>
-    <t>M2-C5</t>
-  </si>
-  <si>
-    <t>M3-C5</t>
-  </si>
-  <si>
-    <t>M4-C5</t>
-  </si>
-  <si>
-    <t>M5-C5</t>
-  </si>
-  <si>
-    <t>M1-C6</t>
-  </si>
-  <si>
-    <t>M2-C6</t>
-  </si>
-  <si>
-    <t>M3-C6</t>
-  </si>
-  <si>
-    <t>M4-C6</t>
-  </si>
-  <si>
-    <t>M5-C6</t>
-  </si>
-  <si>
-    <t>M1-C7</t>
-  </si>
-  <si>
-    <t>M2-C7</t>
-  </si>
-  <si>
-    <t>M3-C7</t>
-  </si>
-  <si>
-    <t>M4-C7</t>
-  </si>
-  <si>
-    <t>M5-C7</t>
-  </si>
-  <si>
-    <t>M1-C8</t>
-  </si>
-  <si>
-    <t>M2-C8</t>
-  </si>
-  <si>
-    <t>M3-C8</t>
-  </si>
-  <si>
-    <t>M4-C8</t>
-  </si>
-  <si>
-    <t>M5-C8</t>
   </si>
   <si>
     <t>Cohort</t>
@@ -169,6 +109,42 @@
   </si>
   <si>
     <t>570M2</t>
+  </si>
+  <si>
+    <t>181M3</t>
+  </si>
+  <si>
+    <t>181M4</t>
+  </si>
+  <si>
+    <t>181M5</t>
+  </si>
+  <si>
+    <t>569M3</t>
+  </si>
+  <si>
+    <t>569M4</t>
+  </si>
+  <si>
+    <t>569M5</t>
+  </si>
+  <si>
+    <t>570M3</t>
+  </si>
+  <si>
+    <t>570M4</t>
+  </si>
+  <si>
+    <t>570M5</t>
+  </si>
+  <si>
+    <t>572M3</t>
+  </si>
+  <si>
+    <t>572M4</t>
+  </si>
+  <si>
+    <t>572M5</t>
   </si>
 </sst>
 </file>
@@ -585,10 +561,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1">
         <v>45609</v>
@@ -599,10 +575,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1">
         <v>45609</v>
@@ -613,10 +589,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1">
         <v>45609</v>
@@ -627,10 +603,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1">
         <v>45609</v>
@@ -641,10 +617,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1">
         <v>45609</v>
@@ -655,10 +631,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1">
         <v>45609</v>
@@ -669,10 +645,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1">
         <v>45609</v>
@@ -683,10 +659,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1">
         <v>45609</v>
@@ -697,10 +673,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C10" s="1">
         <v>45609</v>
@@ -711,10 +687,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C11" s="1">
         <v>45609</v>
@@ -725,10 +701,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C12" s="1">
         <v>45609</v>
@@ -739,10 +715,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1">
         <v>45609</v>
@@ -753,10 +729,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C14" s="1">
         <v>45609</v>
@@ -767,10 +743,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C15" s="1">
         <v>45609</v>
@@ -781,10 +757,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C16" s="1">
         <v>45609</v>
@@ -798,7 +774,7 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C17" s="1">
         <v>45609</v>
@@ -809,10 +785,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C18" s="1">
         <v>45609</v>
@@ -823,10 +799,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C19" s="1">
         <v>45609</v>
@@ -837,10 +813,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C20" s="1">
         <v>45609</v>
@@ -851,10 +827,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C21" s="1">
         <v>45609</v>
@@ -865,10 +841,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C22" s="1">
         <v>45614</v>
@@ -879,10 +855,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1">
         <v>45614</v>
@@ -893,10 +869,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1">
         <v>45614</v>
@@ -907,10 +883,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C25" s="1">
         <v>45614</v>
@@ -921,10 +897,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C26" s="1">
         <v>45614</v>
@@ -935,10 +911,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C27" s="1">
         <v>45614</v>
@@ -949,10 +925,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C28" s="1">
         <v>45614</v>
@@ -963,10 +939,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C29" s="1">
         <v>45614</v>
@@ -977,10 +953,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C30" s="1">
         <v>45614</v>
@@ -991,10 +967,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B31" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C31" s="1">
         <v>45614</v>
@@ -1005,10 +981,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C32" s="1">
         <v>45614</v>
@@ -1019,10 +995,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B33" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C33" s="1">
         <v>45614</v>
@@ -1033,10 +1009,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B34" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C34" s="1">
         <v>45614</v>
@@ -1047,10 +1023,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C35" s="1">
         <v>45614</v>
@@ -1061,10 +1037,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C36" s="1">
         <v>45614</v>
@@ -1078,7 +1054,7 @@
         <v>19</v>
       </c>
       <c r="B37" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C37" s="1">
         <v>45614</v>
@@ -1089,10 +1065,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C38" s="1">
         <v>45614</v>
@@ -1103,10 +1079,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B39" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C39" s="1">
         <v>45614</v>
@@ -1117,10 +1093,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C40" s="1">
         <v>45614</v>
@@ -1131,10 +1107,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B41" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C41" s="1">
         <v>45614</v>
@@ -1145,10 +1121,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C42" s="1">
         <v>45621</v>
@@ -1159,10 +1135,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C43" s="1">
         <v>45621</v>
@@ -1173,10 +1149,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="B44" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C44" s="1">
         <v>45621</v>
@@ -1187,10 +1163,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B45" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C45" s="1">
         <v>45621</v>
@@ -1201,10 +1177,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B46" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C46" s="1">
         <v>45621</v>
@@ -1215,10 +1191,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B47" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C47" s="1">
         <v>45621</v>
@@ -1229,10 +1205,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B48" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C48" s="1">
         <v>45621</v>
@@ -1243,10 +1219,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C49" s="1">
         <v>45621</v>
@@ -1257,10 +1233,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C50" s="1">
         <v>45621</v>
@@ -1271,10 +1247,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B51" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C51" s="1">
         <v>45621</v>
@@ -1285,10 +1261,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B52" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C52" s="1">
         <v>45621</v>
@@ -1299,10 +1275,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B53" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C53" s="1">
         <v>45621</v>
@@ -1313,10 +1289,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C54" s="1">
         <v>45621</v>
@@ -1327,10 +1303,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B55" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C55" s="1">
         <v>45621</v>
@@ -1341,10 +1317,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B56" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C56" s="1">
         <v>45621</v>
@@ -1358,7 +1334,7 @@
         <v>19</v>
       </c>
       <c r="B57" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C57" s="1">
         <v>45621</v>
@@ -1369,10 +1345,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B58" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C58" s="1">
         <v>45621</v>
@@ -1383,10 +1359,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B59" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C59" s="1">
         <v>45621</v>
@@ -1397,10 +1373,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B60" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C60" s="1">
         <v>45621</v>
@@ -1411,10 +1387,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B61" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C61" s="1">
         <v>45621</v>
@@ -1425,10 +1401,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C62" s="1">
         <v>45624</v>
@@ -1439,10 +1415,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B63" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C63" s="1">
         <v>45624</v>
@@ -1453,10 +1429,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C64" s="1">
         <v>45624</v>
@@ -1467,10 +1443,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B65" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C65" s="1">
         <v>45624</v>
@@ -1481,10 +1457,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B66" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C66" s="1">
         <v>45624</v>
@@ -1495,10 +1471,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B67" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C67" s="1">
         <v>45624</v>
@@ -1509,10 +1485,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B68" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C68" s="1">
         <v>45624</v>
@@ -1523,10 +1499,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B69" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C69" s="1">
         <v>45624</v>
@@ -1537,10 +1513,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B70" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C70" s="1">
         <v>45624</v>
@@ -1551,10 +1527,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B71" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C71" s="1">
         <v>45624</v>
@@ -1565,10 +1541,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B72" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C72" s="1">
         <v>45624</v>
@@ -1579,10 +1555,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B73" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C73" s="1">
         <v>45624</v>
@@ -1593,10 +1569,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B74" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C74" s="1">
         <v>45624</v>
@@ -1607,10 +1583,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B75" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C75" s="1">
         <v>45624</v>
@@ -1621,10 +1597,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B76" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C76" s="1">
         <v>45624</v>
@@ -1638,7 +1614,7 @@
         <v>19</v>
       </c>
       <c r="B77" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C77" s="1">
         <v>45624</v>
@@ -1649,10 +1625,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B78" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C78" s="1">
         <v>45624</v>
@@ -1663,10 +1639,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B79" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C79" s="1">
         <v>45624</v>
@@ -1677,10 +1653,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B80" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C80" s="1">
         <v>45624</v>
@@ -1691,10 +1667,10 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B81" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C81" s="1">
         <v>45624</v>
@@ -1705,10 +1681,10 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B82" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C82" s="1">
         <v>45628</v>
@@ -1719,10 +1695,10 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B83" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C83" s="1">
         <v>45628</v>
@@ -1733,10 +1709,10 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="B84" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C84" s="1">
         <v>45628</v>
@@ -1747,10 +1723,10 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B85" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C85" s="1">
         <v>45628</v>
@@ -1761,10 +1737,10 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B86" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C86" s="1">
         <v>45628</v>
@@ -1775,10 +1751,10 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B87" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C87" s="1">
         <v>45628</v>
@@ -1789,10 +1765,10 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B88" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C88" s="1">
         <v>45628</v>
@@ -1803,10 +1779,10 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B89" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C89" s="1">
         <v>45628</v>
@@ -1817,10 +1793,10 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B90" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C90" s="1">
         <v>45628</v>
@@ -1831,10 +1807,10 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B91" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C91" s="1">
         <v>45628</v>
@@ -1845,10 +1821,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B92" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C92" s="1">
         <v>45628</v>
@@ -1859,10 +1835,10 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B93" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C93" s="1">
         <v>45628</v>
@@ -1873,10 +1849,10 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B94" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C94" s="1">
         <v>45628</v>
@@ -1887,10 +1863,10 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B95" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C95" s="1">
         <v>45628</v>
@@ -1901,10 +1877,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B96" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C96" s="1">
         <v>45628</v>
@@ -1918,7 +1894,7 @@
         <v>19</v>
       </c>
       <c r="B97" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C97" s="1">
         <v>45628</v>
@@ -1929,10 +1905,10 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B98" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C98" s="1">
         <v>45628</v>
@@ -1943,10 +1919,10 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B99" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C99" s="1">
         <v>45628</v>
@@ -1957,10 +1933,10 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B100" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C100" s="1">
         <v>45628</v>
@@ -1971,10 +1947,10 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B101" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C101" s="1">
         <v>45628</v>
@@ -1985,10 +1961,10 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B102" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C102" s="1">
         <v>45631</v>
@@ -1999,10 +1975,10 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B103" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C103" s="1">
         <v>45631</v>
@@ -2013,10 +1989,10 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="B104" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C104" s="1">
         <v>45631</v>
@@ -2027,10 +2003,10 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B105" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C105" s="1">
         <v>45631</v>
@@ -2041,10 +2017,10 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B106" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C106" s="1">
         <v>45631</v>
@@ -2055,10 +2031,10 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B107" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C107" s="1">
         <v>45631</v>
@@ -2069,10 +2045,10 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B108" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C108" s="1">
         <v>45631</v>
@@ -2083,10 +2059,10 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B109" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C109" s="1">
         <v>45631</v>
@@ -2097,10 +2073,10 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B110" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C110" s="1">
         <v>45631</v>
@@ -2111,10 +2087,10 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B111" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C111" s="1">
         <v>45631</v>
@@ -2125,10 +2101,10 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B112" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C112" s="1">
         <v>45631</v>
@@ -2139,10 +2115,10 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B113" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C113" s="1">
         <v>45631</v>
@@ -2153,10 +2129,10 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B114" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C114" s="1">
         <v>45631</v>
@@ -2167,10 +2143,10 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B115" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C115" s="1">
         <v>45631</v>
@@ -2181,10 +2157,10 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B116" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C116" s="1">
         <v>45631</v>
@@ -2198,7 +2174,7 @@
         <v>19</v>
       </c>
       <c r="B117" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C117" s="1">
         <v>45631</v>
@@ -2209,10 +2185,10 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B118" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C118" s="1">
         <v>45631</v>
@@ -2223,10 +2199,10 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B119" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C119" s="1">
         <v>45631</v>
@@ -2237,10 +2213,10 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B120" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C120" s="1">
         <v>45631</v>
@@ -2251,10 +2227,10 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B121" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C121" s="1">
         <v>45631</v>
@@ -2265,10 +2241,10 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B122" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C122" s="1">
         <v>45635</v>
@@ -2279,10 +2255,10 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B123" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C123" s="1">
         <v>45635</v>
@@ -2293,10 +2269,10 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="B124" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C124" s="1">
         <v>45635</v>
@@ -2307,10 +2283,10 @@
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B125" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C125" s="1">
         <v>45635</v>
@@ -2321,10 +2297,10 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B126" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C126" s="1">
         <v>45635</v>
@@ -2335,10 +2311,10 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B127" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C127" s="1">
         <v>45635</v>
@@ -2349,10 +2325,10 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B128" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C128" s="1">
         <v>45635</v>
@@ -2363,10 +2339,10 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B129" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C129" s="1">
         <v>45635</v>
@@ -2377,10 +2353,10 @@
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B130" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C130" s="1">
         <v>45635</v>
@@ -2391,10 +2367,10 @@
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B131" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C131" s="1">
         <v>45635</v>
@@ -2405,10 +2381,10 @@
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B132" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C132" s="1">
         <v>45635</v>
@@ -2419,10 +2395,10 @@
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B133" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C133" s="1">
         <v>45635</v>
@@ -2433,10 +2409,10 @@
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B134" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C134" s="1">
         <v>45635</v>
@@ -2447,10 +2423,10 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B135" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C135" s="1">
         <v>45635</v>
@@ -2461,10 +2437,10 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B136" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C136" s="1">
         <v>45635</v>
@@ -2478,7 +2454,7 @@
         <v>19</v>
       </c>
       <c r="B137" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C137" s="1">
         <v>45635</v>
@@ -2489,10 +2465,10 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B138" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C138" s="1">
         <v>45635</v>
@@ -2503,10 +2479,10 @@
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B139" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C139" s="1">
         <v>45635</v>
@@ -2517,10 +2493,10 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B140" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C140" s="1">
         <v>45635</v>
@@ -2531,10 +2507,10 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B141" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C141" s="1">
         <v>45635</v>
@@ -2545,10 +2521,10 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B142" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C142" s="1">
         <v>45664</v>
@@ -2559,10 +2535,10 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B143" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C143" s="1">
         <v>45664</v>
@@ -2573,10 +2549,10 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="B144" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C144" s="1">
         <v>45664</v>
@@ -2587,10 +2563,10 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B145" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C145" s="1">
         <v>45664</v>
@@ -2601,10 +2577,10 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B146" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C146" s="1">
         <v>45664</v>
@@ -2615,10 +2591,10 @@
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B147" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C147" s="1">
         <v>45664</v>
@@ -2629,10 +2605,10 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B148" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C148" s="1">
         <v>45664</v>
@@ -2643,10 +2619,10 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B149" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C149" s="1">
         <v>45664</v>
@@ -2657,10 +2633,10 @@
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B150" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C150" s="1">
         <v>45664</v>
@@ -2671,10 +2647,10 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B151" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="C151" s="1">
         <v>45664</v>
@@ -2685,10 +2661,10 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B152" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C152" s="1">
         <v>45664</v>
@@ -2699,10 +2675,10 @@
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B153" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C153" s="1">
         <v>45664</v>
@@ -2713,10 +2689,10 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B154" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C154" s="1">
         <v>45664</v>
@@ -2727,10 +2703,10 @@
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B155" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C155" s="1">
         <v>45664</v>
@@ -2741,10 +2717,10 @@
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B156" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C156" s="1">
         <v>45664</v>
@@ -2758,7 +2734,7 @@
         <v>19</v>
       </c>
       <c r="B157" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C157" s="1">
         <v>45664</v>
@@ -2769,10 +2745,10 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B158" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C158" s="1">
         <v>45664</v>
@@ -2783,10 +2759,10 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B159" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C159" s="1">
         <v>45664</v>
@@ -2797,10 +2773,10 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B160" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C160" s="1">
         <v>45664</v>
@@ -2811,10 +2787,10 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B161" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C161" s="1">
         <v>45664</v>
@@ -2835,30 +2811,30 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -2869,13 +2845,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -2886,13 +2862,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -2903,13 +2879,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -2920,13 +2896,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -2937,13 +2913,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -2954,13 +2930,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -2971,13 +2947,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -2988,13 +2964,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -3005,13 +2981,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -3022,13 +2998,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -3039,13 +3015,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -3056,13 +3032,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -3073,13 +3049,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -3090,13 +3066,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -3107,13 +3083,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -3124,13 +3100,13 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -3141,13 +3117,13 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -3158,13 +3134,13 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D20">
         <v>15</v>
@@ -3175,13 +3151,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D21">
         <v>15</v>
@@ -3192,13 +3168,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D22">
         <v>15</v>
@@ -3209,13 +3185,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B23" t="s">
         <v>19</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D23">
         <v>15</v>
@@ -3226,13 +3202,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D24">
         <v>15</v>
@@ -3243,13 +3219,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D25">
         <v>15</v>
@@ -3260,13 +3236,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D26">
         <v>15</v>
@@ -3277,13 +3253,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D27">
         <v>15</v>
@@ -3294,13 +3270,13 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C28" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D28">
         <v>15</v>
@@ -3311,13 +3287,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D29">
         <v>15</v>
@@ -3328,13 +3304,13 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D30">
         <v>15</v>
@@ -3345,13 +3321,13 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D31">
         <v>15</v>
@@ -3362,13 +3338,13 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C32" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D32">
         <v>15</v>
@@ -3379,13 +3355,13 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C33" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D33">
         <v>15</v>
@@ -3396,13 +3372,13 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C34" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D34">
         <v>15</v>
@@ -3413,13 +3389,13 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D35">
         <v>15</v>
@@ -3430,13 +3406,13 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B36" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D36">
         <v>15</v>
@@ -3447,13 +3423,13 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C37" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D37">
         <v>15</v>
@@ -3464,13 +3440,13 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D38">
         <v>30</v>
@@ -3481,13 +3457,13 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C39" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D39">
         <v>30</v>
@@ -3498,13 +3474,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C40" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D40">
         <v>30</v>
@@ -3515,13 +3491,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B41" t="s">
         <v>19</v>
       </c>
       <c r="C41" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D41">
         <v>30</v>
@@ -3532,13 +3508,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B42" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C42" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D42">
         <v>30</v>
@@ -3549,13 +3525,13 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C43" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D43">
         <v>30</v>
@@ -3566,13 +3542,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C44" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D44">
         <v>30</v>
@@ -3583,13 +3559,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C45" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D45">
         <v>30</v>
@@ -3600,13 +3576,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B46" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C46" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D46">
         <v>30</v>
@@ -3617,13 +3593,13 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C47" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D47">
         <v>30</v>
@@ -3634,13 +3610,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B48" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C48" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D48">
         <v>30</v>
@@ -3651,13 +3627,13 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B49" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C49" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D49">
         <v>30</v>
@@ -3668,13 +3644,13 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B50" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C50" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D50">
         <v>30</v>
@@ -3685,13 +3661,13 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C51" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D51">
         <v>30</v>
@@ -3702,13 +3678,13 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D52">
         <v>30</v>
@@ -3719,13 +3695,13 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D53">
         <v>30</v>
@@ -3736,13 +3712,13 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B54" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C54" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D54">
         <v>30</v>
@@ -3753,13 +3729,13 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B55" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C55" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D55">
         <v>30</v>
@@ -3770,13 +3746,13 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B56" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C56" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D56">
         <v>60</v>
@@ -3787,13 +3763,13 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C57" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D57">
         <v>60</v>
@@ -3804,13 +3780,13 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C58" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D58">
         <v>60</v>
@@ -3821,13 +3797,13 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B59" t="s">
         <v>19</v>
       </c>
       <c r="C59" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D59">
         <v>60</v>
@@ -3838,13 +3814,13 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B60" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C60" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D60">
         <v>60</v>
@@ -3855,13 +3831,13 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C61" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D61">
         <v>60</v>
@@ -3872,13 +3848,13 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C62" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D62">
         <v>60</v>
@@ -3889,13 +3865,13 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B63" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C63" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D63">
         <v>60</v>
@@ -3906,13 +3882,13 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B64" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C64" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D64">
         <v>60</v>
@@ -3923,13 +3899,13 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C65" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D65">
         <v>60</v>
@@ -3940,13 +3916,13 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B66" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C66" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D66">
         <v>60</v>
@@ -3957,13 +3933,13 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B67" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C67" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D67">
         <v>60</v>
@@ -3974,13 +3950,13 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B68" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C68" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D68">
         <v>60</v>
@@ -3991,13 +3967,13 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C69" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D69">
         <v>60</v>
@@ -4008,13 +3984,13 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C70" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D70">
         <v>60</v>
@@ -4025,13 +4001,13 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B71" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C71" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D71">
         <v>60</v>
@@ -4042,13 +4018,13 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B72" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C72" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D72">
         <v>60</v>
@@ -4059,13 +4035,13 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B73" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C73" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D73">
         <v>60</v>
@@ -4076,13 +4052,13 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B74" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C74" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D74">
         <v>90</v>
@@ -4093,13 +4069,13 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C75" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D75">
         <v>90</v>
@@ -4110,13 +4086,13 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B76" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C76" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D76">
         <v>90</v>
@@ -4127,13 +4103,13 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B77" t="s">
         <v>19</v>
       </c>
       <c r="C77" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D77">
         <v>90</v>
@@ -4144,13 +4120,13 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B78" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C78" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D78">
         <v>90</v>
@@ -4161,13 +4137,13 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C79" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D79">
         <v>90</v>
@@ -4178,13 +4154,13 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B80" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C80" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D80">
         <v>90</v>
@@ -4195,13 +4171,13 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B81" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C81" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D81">
         <v>90</v>
@@ -4212,13 +4188,13 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B82" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C82" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D82">
         <v>90</v>
@@ -4229,13 +4205,13 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C83" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D83">
         <v>90</v>
@@ -4246,13 +4222,13 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B84" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C84" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D84">
         <v>90</v>
@@ -4263,13 +4239,13 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B85" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C85" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D85">
         <v>90</v>
@@ -4280,13 +4256,13 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C86" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D86">
         <v>90</v>
@@ -4297,13 +4273,13 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C87" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D87">
         <v>90</v>
@@ -4314,13 +4290,13 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B88" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C88" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D88">
         <v>90</v>
@@ -4331,13 +4307,13 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B89" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C89" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D89">
         <v>90</v>
@@ -4348,13 +4324,13 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B90" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C90" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D90">
         <v>90</v>
@@ -4365,13 +4341,13 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C91" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D91">
         <v>90</v>
@@ -4382,13 +4358,13 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C92" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D92">
         <v>120</v>
@@ -4399,13 +4375,13 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C93" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D93">
         <v>120</v>
@@ -4416,13 +4392,13 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B94" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C94" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D94">
         <v>120</v>
@@ -4433,13 +4409,13 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B95" t="s">
         <v>19</v>
       </c>
       <c r="C95" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D95">
         <v>120</v>
@@ -4450,13 +4426,13 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B96" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="C96" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D96">
         <v>120</v>
@@ -4467,13 +4443,13 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C97" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D97">
         <v>120</v>
@@ -4484,13 +4460,13 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B98" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C98" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D98">
         <v>120</v>
@@ -4501,13 +4477,13 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B99" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C99" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D99">
         <v>120</v>
@@ -4518,13 +4494,13 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B100" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C100" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D100">
         <v>120</v>
@@ -4535,13 +4511,13 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C101" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D101">
         <v>120</v>
@@ -4552,13 +4528,13 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B102" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C102" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D102">
         <v>120</v>
@@ -4569,13 +4545,13 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B103" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C103" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D103">
         <v>120</v>
@@ -4586,13 +4562,13 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B104" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="C104" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D104">
         <v>120</v>
@@ -4603,13 +4579,13 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C105" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D105">
         <v>120</v>
@@ -4620,13 +4596,13 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B106" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C106" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D106">
         <v>120</v>
@@ -4637,13 +4613,13 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B107" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C107" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D107">
         <v>120</v>
@@ -4654,13 +4630,13 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B108" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C108" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D108">
         <v>120</v>
@@ -4671,13 +4647,13 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="C109" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="D109">
         <v>120</v>

--- a/Data/Figure 3/Mouse weight & GTT/Weight&GTTCohort3.xlsx
+++ b/Data/Figure 3/Mouse weight & GTT/Weight&GTTCohort3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026\Data\Figure 3\Mouse weight &amp; GTT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D44538-31DE-4864-BDE3-543D651FBA19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433EA236-1D45-4C7D-AE34-D9235AA25543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A514A187-A7D1-4A2E-BBE9-38EB1CA0002D}"/>
   </bookViews>

--- a/Data/Figure 3/Mouse weight & GTT/Weight&GTTCohort3.xlsx
+++ b/Data/Figure 3/Mouse weight & GTT/Weight&GTTCohort3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026\Data\Figure 3\Mouse weight &amp; GTT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433EA236-1D45-4C7D-AE34-D9235AA25543}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12644FB-83DC-437F-BFDA-C1B5E0F177DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A514A187-A7D1-4A2E-BBE9-38EB1CA0002D}"/>
   </bookViews>
@@ -3052,7 +3052,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
         <v>15</v>
@@ -3358,7 +3358,7 @@
         <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C33" t="s">
         <v>15</v>
@@ -3664,7 +3664,7 @@
         <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C51" t="s">
         <v>15</v>
@@ -3970,7 +3970,7 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C69" t="s">
         <v>15</v>
@@ -4276,7 +4276,7 @@
         <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C87" t="s">
         <v>15</v>
@@ -4582,7 +4582,7 @@
         <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C105" t="s">
         <v>15</v>
